--- a/data/trans_dic/P36$nada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36$nada-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no desayuna</t>
+          <t>Población que no desayuna (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,37 +678,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,15</t>
+          <t>0,99; 2,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,62</t>
+          <t>1,05; 3,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,41</t>
+          <t>1,6; 4,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,41</t>
+          <t>0,69; 2,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,82</t>
+          <t>0,31; 1,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,45</t>
+          <t>0,65; 2,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,41</t>
+          <t>1,09; 2,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,99</t>
+          <t>1,29; 2,86</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,02</t>
+          <t>1,28; 3,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,64</t>
+          <t>1,4; 3,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,89</t>
+          <t>1,12; 3,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,53</t>
+          <t>0,9; 2,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,63</t>
+          <t>0,87; 2,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,08</t>
+          <t>0,64; 1,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,4</t>
+          <t>1,21; 2,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,75</t>
+          <t>1,27; 2,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,14</t>
+          <t>1,04; 2,22</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,81</t>
+          <t>1,39; 3,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,04</t>
+          <t>1,52; 4,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,87</t>
+          <t>0,8; 2,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,89</t>
+          <t>0,88; 2,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,65</t>
+          <t>1,36; 4,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,8</t>
+          <t>0,38; 1,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,89</t>
+          <t>1,31; 2,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,34</t>
+          <t>1,7; 3,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,97</t>
+          <t>0,73; 1,93</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,15</t>
+          <t>1,36; 3,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,18</t>
+          <t>2,31; 5,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,47</t>
+          <t>0,9; 2,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,72</t>
+          <t>1,06; 2,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,07</t>
+          <t>1,24; 3,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,5</t>
+          <t>0,29; 1,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,62</t>
+          <t>1,37; 2,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,47</t>
+          <t>2,0; 3,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,71</t>
+          <t>0,72; 1,66</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,63</t>
+          <t>1,59; 2,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,27</t>
+          <t>2,02; 3,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,46</t>
+          <t>1,47; 2,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,03</t>
+          <t>1,17; 2,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,27</t>
+          <t>1,31; 2,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,39</t>
+          <t>0,71; 1,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,21</t>
+          <t>1,53; 2,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,57</t>
+          <t>1,8; 2,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,81</t>
+          <t>1,17; 1,72</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no desayuna</t>
+          <t>Población que no desayuna (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6869; 21823</t>
+          <t>6835; 20405</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8170; 25406</t>
+          <t>7379; 23599</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11276; 29668</t>
+          <t>10763; 29196</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4684; 16570</t>
+          <t>4742; 17541</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2186; 12658</t>
+          <t>2139; 11875</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4391; 16462</t>
+          <t>4373; 15910</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14751; 33249</t>
+          <t>15033; 34779</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13211; 32969</t>
+          <t>13210; 33049</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17287; 40231</t>
+          <t>17338; 38524</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11558; 28967</t>
+          <t>12276; 30494</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14038; 37030</t>
+          <t>14294; 37997</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11439; 29544</t>
+          <t>11469; 31187</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8289; 24486</t>
+          <t>8724; 23864</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8931; 27087</t>
+          <t>8965; 27291</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6703; 21721</t>
+          <t>6631; 20718</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23744; 46293</t>
+          <t>23259; 47674</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28057; 56256</t>
+          <t>26087; 54377</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20394; 44166</t>
+          <t>21415; 45754</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8646; 25790</t>
+          <t>9404; 25847</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11689; 30492</t>
+          <t>11518; 30567</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6403; 21735</t>
+          <t>6099; 21402</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5653; 19781</t>
+          <t>6007; 19538</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10526; 28325</t>
+          <t>10543; 31188</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2965; 14093</t>
+          <t>2945; 13078</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17145; 39298</t>
+          <t>17860; 40577</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26238; 51188</t>
+          <t>26041; 51147</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11083; 30478</t>
+          <t>11267; 29791</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12840; 29612</t>
+          <t>12754; 29036</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21900; 48997</t>
+          <t>21885; 47664</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8248; 23116</t>
+          <t>8438; 23833</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10589; 28220</t>
+          <t>10936; 27192</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13105; 32251</t>
+          <t>13008; 31664</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3449; 15590</t>
+          <t>3033; 15399</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27194; 51806</t>
+          <t>27040; 49576</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39168; 69298</t>
+          <t>40002; 70677</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14761; 33828</t>
+          <t>14345; 32847</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>53617; 86118</t>
+          <t>52059; 85648</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>71506; 111914</t>
+          <t>68931; 110026</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49617; 83495</t>
+          <t>49710; 84215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40235; 68593</t>
+          <t>39420; 69792</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>46793; 80458</t>
+          <t>46694; 78507</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25658; 49321</t>
+          <t>25221; 49154</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>100811; 146599</t>
+          <t>101491; 145377</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>126625; 179043</t>
+          <t>125629; 183500</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>80945; 125550</t>
+          <t>81086; 119229</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$nada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36$nada-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,94</t>
+          <t>1,1; 3,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,36</t>
+          <t>1,07; 3,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,34</t>
+          <t>1,61; 4,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,55</t>
+          <t>0,78; 2,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,71</t>
+          <t>0,43; 1,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,37</t>
+          <t>0,65; 2,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,52</t>
+          <t>1,07; 2,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,36</t>
+          <t>0,91; 2,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,86</t>
+          <t>1,31; 2,98</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,18</t>
+          <t>1,2; 3,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,73</t>
+          <t>1,39; 3,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,05</t>
+          <t>1,03; 2,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,47</t>
+          <t>0,9; 2,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,65</t>
+          <t>0,92; 2,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,99</t>
+          <t>0,63; 2,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,47</t>
+          <t>1,28; 2,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,66</t>
+          <t>1,31; 2,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,22</t>
+          <t>1,04; 2,15</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,82</t>
+          <t>1,39; 3,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,05</t>
+          <t>1,55; 4,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,82</t>
+          <t>0,79; 2,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,86</t>
+          <t>0,88; 2,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,02</t>
+          <t>1,41; 3,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,67</t>
+          <t>0,37; 1,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,98</t>
+          <t>1,35; 2,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,34</t>
+          <t>1,75; 3,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,93</t>
+          <t>0,76; 1,93</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,09</t>
+          <t>1,3; 3,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,04</t>
+          <t>2,3; 5,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,54</t>
+          <t>0,91; 2,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,63</t>
+          <t>1,02; 2,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,02</t>
+          <t>1,22; 2,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,48</t>
+          <t>0,28; 1,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,51</t>
+          <t>1,39; 2,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,54</t>
+          <t>1,99; 3,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,66</t>
+          <t>0,73; 1,7</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,62</t>
+          <t>1,6; 2,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,22</t>
+          <t>2,09; 3,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,48</t>
+          <t>1,47; 2,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,07</t>
+          <t>1,22; 2,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,21</t>
+          <t>1,32; 2,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,39</t>
+          <t>0,7; 1,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,19</t>
+          <t>1,53; 2,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,63</t>
+          <t>1,83; 2,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,72</t>
+          <t>1,17; 1,74</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6835; 20405</t>
+          <t>7608; 22133</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7379; 23599</t>
+          <t>7533; 24903</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10763; 29196</t>
+          <t>10846; 29534</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4742; 17541</t>
+          <t>5363; 18240</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2139; 11875</t>
+          <t>3009; 13571</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4373; 15910</t>
+          <t>4358; 16373</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15033; 34779</t>
+          <t>14736; 32397</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13210; 33049</t>
+          <t>12766; 31523</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17338; 38524</t>
+          <t>17620; 40037</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12276; 30494</t>
+          <t>11549; 29615</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14294; 37997</t>
+          <t>14116; 36143</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11469; 31187</t>
+          <t>10479; 30022</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8724; 23864</t>
+          <t>8722; 26317</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8965; 27291</t>
+          <t>9434; 26228</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6631; 20718</t>
+          <t>6517; 20974</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23259; 47674</t>
+          <t>24598; 48183</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26087; 54377</t>
+          <t>26781; 54024</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21415; 45754</t>
+          <t>21522; 44355</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9404; 25847</t>
+          <t>9393; 25790</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11518; 30567</t>
+          <t>11682; 30795</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6099; 21402</t>
+          <t>6011; 21865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6007; 19538</t>
+          <t>6034; 20296</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10543; 31188</t>
+          <t>10955; 29516</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2945; 13078</t>
+          <t>2933; 13339</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17860; 40577</t>
+          <t>18437; 38402</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26041; 51147</t>
+          <t>26803; 51610</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11267; 29791</t>
+          <t>11744; 29811</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12754; 29036</t>
+          <t>12197; 29353</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21885; 47664</t>
+          <t>21716; 48183</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8438; 23833</t>
+          <t>8538; 24364</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10936; 27192</t>
+          <t>10529; 27985</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13008; 31664</t>
+          <t>12787; 31173</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3033; 15399</t>
+          <t>2886; 14435</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27040; 49576</t>
+          <t>27456; 50778</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40002; 70677</t>
+          <t>39806; 71248</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14345; 32847</t>
+          <t>14451; 33760</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>52059; 85648</t>
+          <t>52434; 84976</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68931; 110026</t>
+          <t>71506; 112203</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49710; 84215</t>
+          <t>49934; 82559</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39420; 69792</t>
+          <t>41150; 72259</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>46694; 78507</t>
+          <t>47040; 79044</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25221; 49154</t>
+          <t>24758; 48971</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>101491; 145377</t>
+          <t>101631; 144151</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>125629; 183500</t>
+          <t>127785; 179095</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81086; 119229</t>
+          <t>81435; 120669</t>
         </is>
       </c>
     </row>
